--- a/manual_test/sample-new-format-2026-06.xlsx
+++ b/manual_test/sample-new-format-2026-06.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[11111111-22222222, 33333333-44444444]</t>
+          <t>[1111111122222222, 333333334444444455555555, 6666666677777777]</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -599,12 +599,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11600006-00000000-87654321</t>
+          <t>116000060000000087654321</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10300002-00000000-11112222</t>
+          <t>103000020000000011112222</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -758,7 +758,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -809,7 +809,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>1111111122222222</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -860,47 +860,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>33333333-44444444</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>1111111122222222</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>333333334444444455555555</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MEDIA MARKT</t>
+          <t>Hitelkártyaszámla</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VÁSÁRLÁS KÁRTYÁVAL</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Mosógép</t>
-        </is>
-      </c>
+          <t>QVIK  FIZETÉS  BANKON BELÜL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Műszaki cikk</t>
+          <t>Nem kategorizált</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2024011214200012001</t>
+          <t>2024012007320011007</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-01-12 14:20:00</t>
+          <t>2024-01-20 07:32:14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-20</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>-89990</v>
+        <v>-13562</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -911,47 +911,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>33333333-44444444</t>
+          <t>333333334444444455555555</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OTP Bank</t>
+          <t>MEDIA MARKT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KAMATJÓVÁÍRÁS</t>
+          <t>VÁSÁRLÁS KÁRTYÁVAL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Havi kamat</t>
+          <t>Mosógép</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kamat</t>
+          <t>Műszaki cikk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024011811300012002</t>
+          <t>2024011214200012001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024-01-18 11:30:00</t>
+          <t>2024-01-12 14:20:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12.5</v>
+        <v>-89990</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -959,50 +959,50 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
+          <t>333333334444444455555555</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REJTETT SOR</t>
+          <t>OTP Bank</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VÁSÁRLÁS KÁRTYÁVAL</t>
+          <t>KAMATJÓVÁÍRÁS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ez a sor el van rejtve</t>
+          <t>Havi kamat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rejtett</t>
+          <t>Kamat</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2024012216000011098</t>
+          <t>2024011811300012002</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2024-01-22 16:00:00</t>
+          <t>2024-01-18 11:30:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-7777</v>
+        <v>12.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1013,44 +1013,240 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11111111-22222222</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>333333334444444455555555</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1111111122222222</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>PÉLDA JÁNOS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HITELTÖRLESZTÉS BEFIZETÉS / ÁTUTALÁ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HITELTÖRLESZTÉS BEFIZETÉS / ÁTUTALÁS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nem kategorizált</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20240120073000156503925BATCH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2024-01-20 07:30:15</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>13562</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>333333334444444455555555</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BANKKÁRTYA ÉVES DÍJ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BANKKÁRTYA ÉVES DÍJ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BANKKÁRTYA ÉVES DÍJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Egyéb</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20240124074800630315339BATCH</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2024-01-24 07:48:34</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>-6862</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1111111122222222</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>REJTETT SOR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VÁSÁRLÁS KÁRTYÁVAL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ez a sor el van rejtve</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rejtett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024012216000011098</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2024-01-22 16:00:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>-7777</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1111111122222222</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>FÜGGŐ TÉTEL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Nem könyvelt tétel</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Egyéb</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2024012000000011099</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2024-01-20 00:00:00</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J22" t="n">
         <v>-999</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1111111122222222</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zárolt tétel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Egyéb</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024012500000011097</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2024-01-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>-888</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>HUF</t>
         </is>
